--- a/Office_Suites_NYC.xlsx
+++ b/Office_Suites_NYC.xlsx
@@ -8836,7 +8836,7 @@
       </c>
       <c r="O173" s="1" t="inlineStr">
         <is>
-          <t>833-410-3195</t>
+          <t>917-902-4421</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="O174" s="1" t="inlineStr">
         <is>
-          <t>833-410-3195</t>
+          <t>917-902-4421</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="O175" s="1" t="inlineStr">
         <is>
-          <t>833-410-3195</t>
+          <t>917-902-4421</t>
         </is>
       </c>
       <c r="AE175" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="O176" s="1" t="inlineStr">
         <is>
-          <t>833-410-3195</t>
+          <t>917-902-4421</t>
         </is>
       </c>
       <c r="AE176" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="O178" s="1" t="inlineStr">
         <is>
-          <t>646-320-89022</t>
+          <t>646-320-8922</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -9123,12 +9123,17 @@
       </c>
       <c r="M180" s="8" t="inlineStr">
         <is>
-          <t>Yessenia</t>
+          <t>Paul Carter</t>
         </is>
       </c>
       <c r="O180" s="1" t="inlineStr">
         <is>
-          <t>917-574-9011</t>
+          <t>917-374-6111</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>pcarter@corporatesuites.com</t>
         </is>
       </c>
       <c r="U180" s="21" t="n">
@@ -9174,12 +9179,17 @@
       </c>
       <c r="M181" s="8" t="inlineStr">
         <is>
-          <t>Yessenia</t>
+          <t>Paul Carter</t>
         </is>
       </c>
       <c r="O181" s="1" t="inlineStr">
         <is>
-          <t>917-574-9011</t>
+          <t>917-374-6111</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>pcarter@corporatesuites.com</t>
         </is>
       </c>
       <c r="AE181" t="inlineStr">
@@ -9222,12 +9232,17 @@
       </c>
       <c r="M182" s="8" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Paul Carter</t>
         </is>
       </c>
       <c r="O182" s="1" t="inlineStr">
         <is>
-          <t>866-336-4581</t>
+          <t>917-374-6111</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>pcarter@corporatesuites.com</t>
         </is>
       </c>
       <c r="AE182" t="inlineStr">
@@ -9270,12 +9285,17 @@
       </c>
       <c r="M183" s="8" t="inlineStr">
         <is>
-          <t>Yessenia</t>
+          <t>Paul Carter</t>
         </is>
       </c>
       <c r="O183" s="1" t="inlineStr">
         <is>
-          <t>917-574-9011</t>
+          <t>917-374-6111</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>pcarter@corporatesuites.com</t>
         </is>
       </c>
       <c r="U183" t="inlineStr">
@@ -9294,10 +9314,19 @@
         <f>+A184+1</f>
         <v/>
       </c>
-      <c r="M184" s="8" t="n"/>
+      <c r="M184" s="8" t="inlineStr">
+        <is>
+          <t>Paul Carter</t>
+        </is>
+      </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>tel:+18663364581</t>
+          <t>917-374-6111</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>pcarter@corporatesuites.com</t>
         </is>
       </c>
     </row>

--- a/Office_Suites_NYC.xlsx
+++ b/Office_Suites_NYC.xlsx
@@ -696,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH311"/>
+  <dimension ref="A1:AH313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.140625" customWidth="1" min="1" max="2"/>
@@ -849,7 +849,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="n">
         <v>1</v>
@@ -12630,6 +12629,122 @@
       </c>
       <c r="AH311" s="28" t="n">
         <v>46296</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>221</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Select Office Suites</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>90 Broad Street, Floor 2, 3, 10</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Financial District</t>
+        </is>
+      </c>
+      <c r="K312" t="n">
+        <v>10004</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>Rudy Maisto</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>646-461-9802</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>rudy@selectofficesuites.com</t>
+        </is>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>www.selectofficesuites.com</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>Pays 10% commission first year, negotiable after</t>
+        </is>
+      </c>
+      <c r="AE312" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>222</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Select Office Suites</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>1115 Broadway (16 Madison Square West), Floor 9, 10, 11, 12</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Manhattan</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Flatiron District</t>
+        </is>
+      </c>
+      <c r="K313" t="n">
+        <v>10010</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>Rudy Maisto</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>646-461-9802</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>rudy@selectofficesuites.com</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>www.selectofficesuites.com</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>Pays 10% commission first year, negotiable after</t>
+        </is>
+      </c>
+      <c r="AE313" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Office_Suites_NYC.xlsx
+++ b/Office_Suites_NYC.xlsx
@@ -9334,110 +9334,32 @@
         <f>+A185+1</f>
         <v/>
       </c>
-      <c r="C185" s="1" t="inlineStr">
-        <is>
-          <t>Select Office Suites</t>
-        </is>
-      </c>
+      <c r="C185" s="1" t="n"/>
       <c r="D185" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>90 Boad Street, Floor 2, 3, 10</t>
-        </is>
-      </c>
-      <c r="G185" s="1" t="inlineStr">
-        <is>
-          <t>Manhattan</t>
-        </is>
-      </c>
-      <c r="I185" s="1" t="inlineStr">
-        <is>
-          <t>Financial District</t>
-        </is>
-      </c>
-      <c r="K185" s="1" t="n">
-        <v>10004</v>
-      </c>
-      <c r="M185" s="8" t="inlineStr">
-        <is>
-          <t>Rudy Maisto</t>
-        </is>
-      </c>
-      <c r="O185" s="1" t="inlineStr">
-        <is>
-          <t>646-461-9802</t>
-        </is>
-      </c>
-      <c r="Q185" s="2" t="inlineStr">
-        <is>
-          <t>rudy@selectofficesuites.com</t>
-        </is>
-      </c>
-      <c r="U185" t="inlineStr">
-        <is>
-          <t>first year 10% can work out longer term commission</t>
-        </is>
-      </c>
-      <c r="AE185" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G185" s="1" t="n"/>
+      <c r="I185" s="1" t="n"/>
+      <c r="K185" s="1" t="n"/>
+      <c r="M185" s="8" t="n"/>
+      <c r="O185" s="1" t="n"/>
+      <c r="Q185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186">
         <f>+A186+1</f>
         <v/>
       </c>
-      <c r="C186" s="1" t="inlineStr">
-        <is>
-          <t>Select Office Suites</t>
-        </is>
-      </c>
+      <c r="C186" s="1" t="n"/>
       <c r="D186" s="1">
         <f>+D186+1</f>
         <v/>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>1115 Braodway (15 Madison Ave West), Floor 9, 10, 11, 12</t>
-        </is>
-      </c>
-      <c r="G186" s="1" t="inlineStr">
-        <is>
-          <t>Manhattan</t>
-        </is>
-      </c>
-      <c r="I186" s="1" t="inlineStr">
-        <is>
-          <t>Flatiron / NoMad</t>
-        </is>
-      </c>
-      <c r="K186" s="1" t="n">
-        <v>10010</v>
-      </c>
-      <c r="M186" s="8" t="inlineStr">
-        <is>
-          <t>Rudy Maisto</t>
-        </is>
-      </c>
-      <c r="O186" s="1" t="inlineStr">
-        <is>
-          <t>646-461-9802</t>
-        </is>
-      </c>
-      <c r="Q186" t="inlineStr">
-        <is>
-          <t>mailto:rudy@selectofficesuites.com</t>
-        </is>
-      </c>
-      <c r="AE186" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G186" s="1" t="n"/>
+      <c r="I186" s="1" t="n"/>
+      <c r="K186" s="1" t="n"/>
+      <c r="M186" s="8" t="n"/>
+      <c r="O186" s="1" t="n"/>
     </row>
     <row r="187">
       <c r="A187">
@@ -12823,8 +12745,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E183" display="https://www.corporatesuites.com/locations/880-third-avenue-shared-office-space-nyc/" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" display="tel:+18663364581" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O184" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q186" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U189" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U189" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Office_Suites_NYC.xlsx
+++ b/Office_Suites_NYC.xlsx
@@ -901,18 +901,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <f>+A5+1</f>
-        <v/>
+      <c r="A6" t="n">
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D6" s="1">
-        <f>1+D5</f>
-        <v/>
+      <c r="D6" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -949,18 +947,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <f>+A6+1</f>
-        <v/>
+      <c r="A7" t="n">
+        <v>3</v>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D7" s="1">
-        <f>1+D6</f>
-        <v/>
+      <c r="D7" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -997,18 +993,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <f>+A7+1</f>
-        <v/>
+      <c r="A8" t="n">
+        <v>4</v>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D8" s="1">
-        <f>1+D7</f>
-        <v/>
+      <c r="D8" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1050,18 +1044,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <f>+A8+1</f>
-        <v/>
+      <c r="A9" t="n">
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D9" s="1">
-        <f>1+D8</f>
-        <v/>
+      <c r="D9" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1098,18 +1090,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <f>+A9+1</f>
-        <v/>
+      <c r="A10" t="n">
+        <v>6</v>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D10" s="1">
-        <f>1+D9</f>
-        <v/>
+      <c r="D10" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1146,18 +1136,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <f>+A10+1</f>
-        <v/>
+      <c r="A11" t="n">
+        <v>7</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D11" s="1">
-        <f>1+D10</f>
-        <v/>
+      <c r="D11" s="1" t="n">
+        <v>7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1194,18 +1182,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <f>+A11+1</f>
-        <v/>
+      <c r="A12" t="n">
+        <v>8</v>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D12" s="1">
-        <f>1+D11</f>
-        <v/>
+      <c r="D12" s="1" t="n">
+        <v>8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1242,18 +1228,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <f>+A12+1</f>
-        <v/>
+      <c r="A13" t="n">
+        <v>9</v>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D13" s="1">
-        <f>1+D12</f>
-        <v/>
+      <c r="D13" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1290,18 +1274,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <f>+A13+1</f>
-        <v/>
+      <c r="A14" t="n">
+        <v>10</v>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D14" s="1">
-        <f>1+D13</f>
-        <v/>
+      <c r="D14" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1338,22 +1320,20 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <f>+A14+1</f>
-        <v/>
+      <c r="A15" t="n">
+        <v>11</v>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D15" s="1">
-        <f>1+D14</f>
-        <v/>
+      <c r="D15" s="1" t="n">
+        <v>11</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>165 Broadway, Foor 23</t>
+          <t>165 Broadway, Floor 23</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
@@ -1386,18 +1366,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <f>+A15+1</f>
-        <v/>
+      <c r="A16" t="n">
+        <v>12</v>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D16" s="1">
-        <f>1+D15</f>
-        <v/>
+      <c r="D16" s="1" t="n">
+        <v>12</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1434,18 +1412,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <f>+A16+1</f>
-        <v/>
+      <c r="A17" t="n">
+        <v>13</v>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D17" s="1">
-        <f>1+D16</f>
-        <v/>
+      <c r="D17" s="1" t="n">
+        <v>13</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1482,18 +1458,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <f>+A17+1</f>
-        <v/>
+      <c r="A18" t="n">
+        <v>14</v>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D18" s="1">
-        <f>1+D17</f>
-        <v/>
+      <c r="D18" s="1" t="n">
+        <v>14</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1530,18 +1504,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <f>+A18+1</f>
-        <v/>
+      <c r="A19" t="n">
+        <v>15</v>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D19" s="1">
-        <f>1+D18</f>
-        <v/>
+      <c r="D19" s="1" t="n">
+        <v>15</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1555,7 +1527,7 @@
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>Midtown South/Hudson Square</t>
+          <t>Hudson Square</t>
         </is>
       </c>
       <c r="K19" s="1" t="n">
@@ -1578,18 +1550,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <f>+A19+1</f>
-        <v/>
+      <c r="A20" t="n">
+        <v>16</v>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D20" s="1">
-        <f>1+D19</f>
-        <v/>
+      <c r="D20" s="1" t="n">
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1603,7 +1573,7 @@
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>Tribeca/Meat Packing District</t>
+          <t>Tribeca</t>
         </is>
       </c>
       <c r="K20" s="1" t="n">
@@ -1626,18 +1596,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <f>+A20+1</f>
-        <v/>
+      <c r="A21" t="n">
+        <v>17</v>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D21" s="1">
-        <f>1+D20</f>
-        <v/>
+      <c r="D21" s="1" t="n">
+        <v>17</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1674,18 +1642,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <f>+A21+1</f>
-        <v/>
+      <c r="A22" t="n">
+        <v>18</v>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D22" s="1">
-        <f>1+D21</f>
-        <v/>
+      <c r="D22" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1722,18 +1688,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <f>+A22+1</f>
-        <v/>
+      <c r="A23" t="n">
+        <v>19</v>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D23" s="1">
-        <f>1+D22</f>
-        <v/>
+      <c r="D23" s="1" t="n">
+        <v>19</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1770,18 +1734,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <f>+A23+1</f>
-        <v/>
+      <c r="A24" t="n">
+        <v>20</v>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D24" s="1">
-        <f>1+D23</f>
-        <v/>
+      <c r="D24" s="1" t="n">
+        <v>20</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1818,18 +1780,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <f>+A24+1</f>
-        <v/>
+      <c r="A25" t="n">
+        <v>21</v>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D25" s="1">
-        <f>1+D24</f>
-        <v/>
+      <c r="D25" s="1" t="n">
+        <v>21</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1866,18 +1826,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <f>+A25+1</f>
-        <v/>
+      <c r="A26" t="n">
+        <v>22</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D26" s="1">
-        <f>1+D25</f>
-        <v/>
+      <c r="D26" s="1" t="n">
+        <v>22</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1914,18 +1872,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <f>+A26+1</f>
-        <v/>
+      <c r="A27" t="n">
+        <v>23</v>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D27" s="1">
-        <f>1+D26</f>
-        <v/>
+      <c r="D27" s="1" t="n">
+        <v>23</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1962,18 +1918,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <f>+A27+1</f>
-        <v/>
+      <c r="A28" t="n">
+        <v>24</v>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D28" s="1">
-        <f>1+D27</f>
-        <v/>
+      <c r="D28" s="1" t="n">
+        <v>24</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2010,18 +1964,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <f>+A28+1</f>
-        <v/>
+      <c r="A29" t="n">
+        <v>25</v>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D29" s="1">
-        <f>1+D28</f>
-        <v/>
+      <c r="D29" s="1" t="n">
+        <v>25</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2058,18 +2010,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <f>+A29+1</f>
-        <v/>
+      <c r="A30" t="n">
+        <v>26</v>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D30" s="1">
-        <f>1+D29</f>
-        <v/>
+      <c r="D30" s="1" t="n">
+        <v>26</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2106,18 +2056,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <f>+A30+1</f>
-        <v/>
+      <c r="A31" t="n">
+        <v>27</v>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D31" s="1">
-        <f>1+D30</f>
-        <v/>
+      <c r="D31" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2154,18 +2102,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <f>+A31+1</f>
-        <v/>
+      <c r="A32" t="n">
+        <v>28</v>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D32" s="1">
-        <f>1+D31</f>
-        <v/>
+      <c r="D32" s="1" t="n">
+        <v>28</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2202,18 +2148,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <f>+A32+1</f>
-        <v/>
+      <c r="A33" t="n">
+        <v>29</v>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D33" s="1">
-        <f>1+D32</f>
-        <v/>
+      <c r="D33" s="1" t="n">
+        <v>29</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2250,18 +2194,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <f>+A33+1</f>
-        <v/>
+      <c r="A34" t="n">
+        <v>30</v>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D34" s="1">
-        <f>1+D33</f>
-        <v/>
+      <c r="D34" s="1" t="n">
+        <v>30</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2275,7 +2217,7 @@
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>Rockefeller Center/ Plaza District</t>
+          <t>Rockefeller Center/Plaza District</t>
         </is>
       </c>
       <c r="K34" s="1" t="n">
@@ -2298,18 +2240,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <f>+A34+1</f>
-        <v/>
+      <c r="A35" t="n">
+        <v>31</v>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D35" s="1">
-        <f>1+D34</f>
-        <v/>
+      <c r="D35" s="1" t="n">
+        <v>31</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2346,18 +2286,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <f>+A35+1</f>
-        <v/>
+      <c r="A36" t="n">
+        <v>32</v>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D36" s="1">
-        <f>1+D35</f>
-        <v/>
+      <c r="D36" s="1" t="n">
+        <v>32</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2394,18 +2332,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <f>+A36+1</f>
-        <v/>
+      <c r="A37" t="n">
+        <v>33</v>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D37" s="1">
-        <f>1+D36</f>
-        <v/>
+      <c r="D37" s="1" t="n">
+        <v>33</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2442,18 +2378,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <f>+A37+1</f>
-        <v/>
+      <c r="A38" t="n">
+        <v>34</v>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D38" s="1">
-        <f>1+D37</f>
-        <v/>
+      <c r="D38" s="1" t="n">
+        <v>34</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2490,18 +2424,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <f>+A38+1</f>
-        <v/>
+      <c r="A39" t="n">
+        <v>35</v>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D39" s="1">
-        <f>1+D38</f>
-        <v/>
+      <c r="D39" s="1" t="n">
+        <v>35</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2538,18 +2470,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <f>+A39+1</f>
-        <v/>
+      <c r="A40" t="n">
+        <v>36</v>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D40" s="1">
-        <f>1+D39</f>
-        <v/>
+      <c r="D40" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2586,18 +2516,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <f>+A40+1</f>
-        <v/>
+      <c r="A41" t="n">
+        <v>37</v>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
           <t>Regus</t>
         </is>
       </c>
-      <c r="D41" s="1">
-        <f>1+D40</f>
-        <v/>
+      <c r="D41" s="1" t="n">
+        <v>37</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2639,16 +2567,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <f>+A41+1</f>
-        <v/>
-      </c>
       <c r="M42" s="8" t="n"/>
     </row>
     <row r="43">
-      <c r="A43">
-        <f>+A42+1</f>
-        <v/>
+      <c r="A43" t="n">
+        <v>38</v>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
@@ -2698,18 +2621,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <f>+A43+1</f>
-        <v/>
+      <c r="A44" t="n">
+        <v>39</v>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
           <t>Bevmax</t>
         </is>
       </c>
-      <c r="D44" s="1">
-        <f>1+D43</f>
-        <v/>
+      <c r="D44" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2746,18 +2667,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <f>+A44+1</f>
-        <v/>
+      <c r="A45" t="n">
+        <v>40</v>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
           <t>Bevmax</t>
         </is>
       </c>
-      <c r="D45" s="1">
-        <f>1+D44</f>
-        <v/>
+      <c r="D45" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2794,18 +2713,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <f>+A46+1</f>
-        <v/>
+      <c r="A46" t="n">
+        <v>41</v>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
           <t>Bevmax</t>
         </is>
       </c>
-      <c r="D46" s="1">
-        <f>1+D46</f>
-        <v/>
+      <c r="D46" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2842,16 +2759,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <f>+A47+1</f>
-        <v/>
-      </c>
       <c r="M47" s="8" t="n"/>
     </row>
     <row r="48">
-      <c r="A48">
-        <f>+A48+1</f>
-        <v/>
+      <c r="A48" t="n">
+        <v>42</v>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
@@ -2901,18 +2813,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <f>+A49+1</f>
-        <v/>
+      <c r="A49" t="n">
+        <v>43</v>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
           <t>JSuites</t>
         </is>
       </c>
-      <c r="D49" s="1">
-        <f>1+D49</f>
-        <v/>
+      <c r="D49" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2959,18 +2869,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <f>+A50+1</f>
-        <v/>
+      <c r="A50" t="n">
+        <v>44</v>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
           <t>JSuites</t>
         </is>
       </c>
-      <c r="D50" s="1">
-        <f>1+D50</f>
-        <v/>
+      <c r="D50" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -3012,18 +2920,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <f>+A51+1</f>
-        <v/>
+      <c r="A51" t="n">
+        <v>45</v>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
           <t>JSuites</t>
         </is>
       </c>
-      <c r="D51" s="1">
-        <f>1+D51</f>
-        <v/>
+      <c r="D51" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3065,18 +2971,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <f>+A52+1</f>
-        <v/>
+      <c r="A52" t="n">
+        <v>46</v>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
           <t>JSuites</t>
         </is>
       </c>
-      <c r="D52" s="1">
-        <f>1+D52</f>
-        <v/>
+      <c r="D52" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -3118,18 +3022,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <f>+A53+1</f>
-        <v/>
+      <c r="A53" t="n">
+        <v>47</v>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
           <t>JSuites</t>
         </is>
       </c>
-      <c r="D53" s="1">
-        <f>1+D53</f>
-        <v/>
+      <c r="D53" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -3171,18 +3073,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54">
-        <f>+A54+1</f>
-        <v/>
+      <c r="A54" t="n">
+        <v>48</v>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
           <t>JSuites</t>
         </is>
       </c>
-      <c r="D54" s="1">
-        <f>1+D54</f>
-        <v/>
+      <c r="D54" s="1" t="n">
+        <v>7</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3224,18 +3124,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55">
-        <f>+A55+1</f>
-        <v/>
+      <c r="A55" t="n">
+        <v>49</v>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
           <t>JSuites</t>
         </is>
       </c>
-      <c r="D55" s="1">
-        <f>1+D55</f>
-        <v/>
+      <c r="D55" s="1" t="n">
+        <v>8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3277,18 +3175,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56">
-        <f>+A56+1</f>
-        <v/>
+      <c r="A56" t="n">
+        <v>50</v>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
           <t>JSuites</t>
         </is>
       </c>
-      <c r="D56" s="1">
-        <f>1+D56</f>
-        <v/>
+      <c r="D56" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3330,18 +3226,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57">
-        <f>+A57+1</f>
-        <v/>
+      <c r="A57" t="n">
+        <v>51</v>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
           <t>JSuites</t>
         </is>
       </c>
-      <c r="D57" s="1">
-        <f>1+D57</f>
-        <v/>
+      <c r="D57" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3383,16 +3277,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58">
-        <f>+A58+1</f>
-        <v/>
-      </c>
       <c r="M58" s="8" t="n"/>
     </row>
     <row r="59">
-      <c r="A59">
-        <f>+A59+1</f>
-        <v/>
+      <c r="A59" t="n">
+        <v>52</v>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
@@ -3447,16 +3336,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60">
-        <f>+A60+1</f>
-        <v/>
-      </c>
       <c r="M60" s="8" t="n"/>
     </row>
     <row r="61">
-      <c r="A61">
-        <f>+A61+1</f>
-        <v/>
+      <c r="A61" t="n">
+        <v>53</v>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
@@ -3502,18 +3386,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62">
-        <f>+A62+1</f>
-        <v/>
+      <c r="A62" t="n">
+        <v>54</v>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
           <t>NYC Office Suites</t>
         </is>
       </c>
-      <c r="D62" s="1">
-        <f>1+D62</f>
-        <v/>
+      <c r="D62" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -3551,9 +3433,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63">
-        <f>+A63+1</f>
-        <v/>
+      <c r="A63" t="n">
+        <v>55</v>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
@@ -3561,7 +3442,7 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -3599,18 +3480,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64">
-        <f>+A64+1</f>
-        <v/>
+      <c r="A64" t="n">
+        <v>56</v>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
           <t>NYC Office Suites</t>
         </is>
       </c>
-      <c r="D64" s="1">
-        <f>1+D64</f>
-        <v/>
+      <c r="D64" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3648,9 +3527,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65">
-        <f>+A65+1</f>
-        <v/>
+      <c r="A65" t="n">
+        <v>57</v>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
@@ -3658,7 +3536,7 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3696,18 +3574,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66">
-        <f>+A66+1</f>
-        <v/>
+      <c r="A66" t="n">
+        <v>58</v>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
           <t>NYC Office Suites</t>
         </is>
       </c>
-      <c r="D66" s="1">
-        <f>1+D66</f>
-        <v/>
+      <c r="D66" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3745,16 +3621,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67">
-        <f>+A67+1</f>
-        <v/>
-      </c>
       <c r="M67" s="8" t="n"/>
     </row>
     <row r="68">
-      <c r="A68">
-        <f>+A68+1</f>
-        <v/>
+      <c r="A68" t="n">
+        <v>59</v>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
@@ -3776,7 +3647,7 @@
       </c>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>Time Square</t>
+          <t>Times Square</t>
         </is>
       </c>
       <c r="K68" s="1" t="n">
@@ -3814,9 +3685,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69">
-        <f>+A69+1</f>
-        <v/>
+      <c r="A69" t="n">
+        <v>60</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3836,9 +3709,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70">
-        <f>+A70+1</f>
-        <v/>
+      <c r="A70" t="n">
+        <v>61</v>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
@@ -3898,18 +3770,16 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71">
-        <f>+A71+1</f>
-        <v/>
+      <c r="A71" t="n">
+        <v>62</v>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
           <t>Studio - Tishman Speyer</t>
         </is>
       </c>
-      <c r="D71" s="1">
-        <f>1+D71</f>
-        <v/>
+      <c r="D71" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3961,9 +3831,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72">
-        <f>+A72+1</f>
-        <v/>
+      <c r="A72" t="n">
+        <v>63</v>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
@@ -3971,7 +3840,7 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -4018,18 +3887,16 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73">
-        <f>+A73+1</f>
-        <v/>
+      <c r="A73" t="n">
+        <v>64</v>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
           <t>Studio - Tishman Speyer</t>
         </is>
       </c>
-      <c r="D73" s="1">
-        <f>1+D73</f>
-        <v/>
+      <c r="D73" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -4071,9 +3938,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74">
-        <f>+A74+1</f>
-        <v/>
+      <c r="A74" t="n">
+        <v>65</v>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
@@ -4081,7 +3947,7 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -4123,18 +3989,16 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75">
-        <f>+A75+1</f>
-        <v/>
+      <c r="A75" t="n">
+        <v>66</v>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
           <t>Studio - Tishman Speyer</t>
         </is>
       </c>
-      <c r="D75" s="1">
-        <f>1+D75</f>
-        <v/>
+      <c r="D75" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -4176,9 +4040,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76">
-        <f>+A76+1</f>
-        <v/>
+      <c r="A76" t="n">
+        <v>67</v>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
@@ -4186,7 +4049,7 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -4228,18 +4091,16 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77">
-        <f>+A77+1</f>
-        <v/>
+      <c r="A77" t="n">
+        <v>68</v>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
           <t>Studio - Tishman Speyer</t>
         </is>
       </c>
-      <c r="D77" s="1">
-        <f>1+D77</f>
-        <v/>
+      <c r="D77" s="1" t="n">
+        <v>8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -4281,9 +4142,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78">
-        <f>+A78+1</f>
-        <v/>
+      <c r="A78" t="n">
+        <v>69</v>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
@@ -4291,7 +4151,7 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -4333,18 +4193,16 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79">
-        <f>+A79+1</f>
-        <v/>
+      <c r="A79" t="n">
+        <v>70</v>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
           <t>Studio - Tishman Speyer</t>
         </is>
       </c>
-      <c r="D79" s="1">
-        <f>1+D79</f>
-        <v/>
+      <c r="D79" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -4386,10 +4244,6 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80">
-        <f>+A80+1</f>
-        <v/>
-      </c>
       <c r="M80" s="8" t="n"/>
       <c r="Q80" t="inlineStr">
         <is>
@@ -4398,9 +4252,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81">
-        <f>+A81+1</f>
-        <v/>
+      <c r="A81" t="n">
+        <v>71</v>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
@@ -4455,10 +4308,6 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82">
-        <f>+A82+1</f>
-        <v/>
-      </c>
       <c r="M82" s="8" t="n"/>
       <c r="S82" t="inlineStr">
         <is>
@@ -4467,9 +4316,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83">
-        <f>+A83+1</f>
-        <v/>
+      <c r="A83" t="n">
+        <v>72</v>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
@@ -4529,18 +4377,16 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84">
-        <f>+A84+1</f>
-        <v/>
+      <c r="A84" t="n">
+        <v>73</v>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D84" s="1">
-        <f>1+D84</f>
-        <v/>
+      <c r="D84" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4592,18 +4438,16 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85">
-        <f>+A85+1</f>
-        <v/>
+      <c r="A85" t="n">
+        <v>74</v>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D85" s="1">
-        <f>1+D85</f>
-        <v/>
+      <c r="D85" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4645,18 +4489,16 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86">
-        <f>+A86+1</f>
-        <v/>
+      <c r="A86" t="n">
+        <v>75</v>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D86" s="1">
-        <f>1+D86</f>
-        <v/>
+      <c r="D86" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -4698,18 +4540,16 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87">
-        <f>+A87+1</f>
-        <v/>
+      <c r="A87" t="n">
+        <v>76</v>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D87" s="1">
-        <f>1+D87</f>
-        <v/>
+      <c r="D87" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -4751,18 +4591,16 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88">
-        <f>+A88+1</f>
-        <v/>
+      <c r="A88" t="n">
+        <v>77</v>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D88" s="1">
-        <f>1+D88</f>
-        <v/>
+      <c r="D88" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -4804,18 +4642,16 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89">
-        <f>+A89+1</f>
-        <v/>
+      <c r="A89" t="n">
+        <v>78</v>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D89" s="1">
-        <f>1+D89</f>
-        <v/>
+      <c r="D89" s="1" t="n">
+        <v>7</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -4857,18 +4693,16 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90">
-        <f>+A90+1</f>
-        <v/>
+      <c r="A90" t="n">
+        <v>79</v>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D90" s="1">
-        <f>1+D90</f>
-        <v/>
+      <c r="D90" s="1" t="n">
+        <v>8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -4910,18 +4744,16 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91">
-        <f>+A91+1</f>
-        <v/>
+      <c r="A91" t="n">
+        <v>80</v>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D91" s="1">
-        <f>1+D91</f>
-        <v/>
+      <c r="D91" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -4963,18 +4795,16 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92">
-        <f>+A92+1</f>
-        <v/>
+      <c r="A92" t="n">
+        <v>81</v>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D92" s="1">
-        <f>1+D92</f>
-        <v/>
+      <c r="D92" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -5016,18 +4846,16 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93">
-        <f>+A93+1</f>
-        <v/>
+      <c r="A93" t="n">
+        <v>82</v>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D93" s="1">
-        <f>1+D93</f>
-        <v/>
+      <c r="D93" s="1" t="n">
+        <v>11</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -5069,18 +4897,16 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94">
-        <f>+A94+1</f>
-        <v/>
+      <c r="A94" t="n">
+        <v>83</v>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D94" s="1">
-        <f>1+D94</f>
-        <v/>
+      <c r="D94" s="1" t="n">
+        <v>12</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -5122,18 +4948,16 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95">
-        <f>+A95+1</f>
-        <v/>
+      <c r="A95" t="n">
+        <v>84</v>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D95" s="1">
-        <f>1+D95</f>
-        <v/>
+      <c r="D95" s="1" t="n">
+        <v>13</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -5175,18 +4999,16 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96">
-        <f>+A96+1</f>
-        <v/>
+      <c r="A96" t="n">
+        <v>85</v>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D96" s="1">
-        <f>1+D96</f>
-        <v/>
+      <c r="D96" s="1" t="n">
+        <v>14</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -5228,18 +5050,16 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97">
-        <f>+A97+1</f>
-        <v/>
+      <c r="A97" t="n">
+        <v>86</v>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D97" s="1">
-        <f>1+D97</f>
-        <v/>
+      <c r="D97" s="1" t="n">
+        <v>15</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -5281,18 +5101,16 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98">
-        <f>+A98+1</f>
-        <v/>
+      <c r="A98" t="n">
+        <v>87</v>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D98" s="1">
-        <f>1+D98</f>
-        <v/>
+      <c r="D98" s="1" t="n">
+        <v>16</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -5334,18 +5152,16 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99">
-        <f>+A99+1</f>
-        <v/>
+      <c r="A99" t="n">
+        <v>88</v>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D99" s="1">
-        <f>1+D99</f>
-        <v/>
+      <c r="D99" s="1" t="n">
+        <v>17</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -5387,18 +5203,16 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100">
-        <f>+A100+1</f>
-        <v/>
+      <c r="A100" t="n">
+        <v>89</v>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D100" s="1">
-        <f>1+D100</f>
-        <v/>
+      <c r="D100" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -5412,7 +5226,7 @@
       </c>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>SoHo West</t>
+          <t>SoHo</t>
         </is>
       </c>
       <c r="K100" s="1" t="n">
@@ -5440,18 +5254,16 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101">
-        <f>+A101+1</f>
-        <v/>
+      <c r="A101" t="n">
+        <v>90</v>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D101" s="1">
-        <f>1+D101</f>
-        <v/>
+      <c r="D101" s="1" t="n">
+        <v>19</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -5465,7 +5277,7 @@
       </c>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>University Place</t>
+          <t>Union Square</t>
         </is>
       </c>
       <c r="K101" s="1" t="n">
@@ -5493,18 +5305,16 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102">
-        <f>+A102+1</f>
-        <v/>
+      <c r="A102" t="n">
+        <v>91</v>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D102" s="1">
-        <f>1+D102</f>
-        <v/>
+      <c r="D102" s="1" t="n">
+        <v>20</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -5546,18 +5356,16 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103">
-        <f>+A103+1</f>
-        <v/>
+      <c r="A103" t="n">
+        <v>92</v>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D103" s="1">
-        <f>1+D103</f>
-        <v/>
+      <c r="D103" s="1" t="n">
+        <v>21</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -5599,18 +5407,16 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104">
-        <f>+A104+1</f>
-        <v/>
+      <c r="A104" t="n">
+        <v>93</v>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D104" s="1">
-        <f>1+D104</f>
-        <v/>
+      <c r="D104" s="1" t="n">
+        <v>22</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -5652,18 +5458,16 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105">
-        <f>+A105+1</f>
-        <v/>
+      <c r="A105" t="n">
+        <v>94</v>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D105" s="1">
-        <f>1+D105</f>
-        <v/>
+      <c r="D105" s="1" t="n">
+        <v>23</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -5705,18 +5509,16 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106">
-        <f>+A106+1</f>
-        <v/>
+      <c r="A106" t="n">
+        <v>95</v>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D106" s="1">
-        <f>1+D106</f>
-        <v/>
+      <c r="D106" s="1" t="n">
+        <v>24</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -5730,7 +5532,7 @@
       </c>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Flatiron District</t>
         </is>
       </c>
       <c r="K106" s="1" t="n">
@@ -5758,18 +5560,16 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107">
-        <f>+A107+1</f>
-        <v/>
+      <c r="A107" t="n">
+        <v>96</v>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D107" s="1">
-        <f>1+D107</f>
-        <v/>
+      <c r="D107" s="1" t="n">
+        <v>25</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -5811,18 +5611,16 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108">
-        <f>+A108+1</f>
-        <v/>
+      <c r="A108" t="n">
+        <v>97</v>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D108" s="1">
-        <f>1+D108</f>
-        <v/>
+      <c r="D108" s="1" t="n">
+        <v>26</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5864,18 +5662,16 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109">
-        <f>+A109+1</f>
-        <v/>
+      <c r="A109" t="n">
+        <v>98</v>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D109" s="1">
-        <f>1+D109</f>
-        <v/>
+      <c r="D109" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -5917,18 +5713,16 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110">
-        <f>+A110+1</f>
-        <v/>
+      <c r="A110" t="n">
+        <v>99</v>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D110" s="1">
-        <f>1+D110</f>
-        <v/>
+      <c r="D110" s="1" t="n">
+        <v>28</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -5942,7 +5736,7 @@
       </c>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>Penn District</t>
+          <t>Penn Plaza</t>
         </is>
       </c>
       <c r="K110" s="1" t="n">
@@ -5970,18 +5764,16 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111">
-        <f>+A111+1</f>
-        <v/>
+      <c r="A111" t="n">
+        <v>100</v>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D111" s="1">
-        <f>1+D111</f>
-        <v/>
+      <c r="D111" s="1" t="n">
+        <v>29</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -5995,7 +5787,7 @@
       </c>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>Penn District</t>
+          <t>Penn Plaza</t>
         </is>
       </c>
       <c r="K111" s="1" t="n">
@@ -6023,18 +5815,16 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112">
-        <f>+A112+1</f>
-        <v/>
+      <c r="A112" t="n">
+        <v>101</v>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D112" s="1">
-        <f>1+D112</f>
-        <v/>
+      <c r="D112" s="1" t="n">
+        <v>30</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -6076,71 +5866,31 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113">
-        <f>+A113+1</f>
-        <v/>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="A113" t="n">
+        <v>102</v>
+      </c>
+      <c r="C113" s="1" t="n"/>
+      <c r="D113" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="G113" s="1" t="n"/>
+      <c r="I113" s="1" t="n"/>
+      <c r="K113" s="1" t="n"/>
+      <c r="M113" s="8" t="n"/>
+      <c r="O113" s="1" t="n"/>
+      <c r="Q113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>103</v>
+      </c>
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D113" s="1">
-        <f>1+D113</f>
-        <v/>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>119 West 24th Street</t>
-        </is>
-      </c>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>Manhattan</t>
-        </is>
-      </c>
-      <c r="I113" s="1" t="inlineStr">
-        <is>
-          <t>Flatiron</t>
-        </is>
-      </c>
-      <c r="K113" s="1" t="n">
-        <v>10011</v>
-      </c>
-      <c r="M113" s="8" t="inlineStr">
-        <is>
-          <t>Saoirse Kennedy</t>
-        </is>
-      </c>
-      <c r="O113" s="1" t="inlineStr">
-        <is>
-          <t>929-276-8644</t>
-        </is>
-      </c>
-      <c r="Q113" s="2" t="inlineStr">
-        <is>
-          <t>brokers@industriousoffice.com</t>
-        </is>
-      </c>
-      <c r="AE113" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114">
-        <f>+A114+1</f>
-        <v/>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>Industrious</t>
-        </is>
-      </c>
-      <c r="D114" s="1">
-        <f>1+D114</f>
-        <v/>
+      <c r="D114" s="1" t="n">
+        <v>32</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -6182,18 +5932,16 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115">
-        <f>+A115+1</f>
-        <v/>
+      <c r="A115" t="n">
+        <v>104</v>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D115" s="1">
-        <f>1+D115</f>
-        <v/>
+      <c r="D115" s="1" t="n">
+        <v>33</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -6207,7 +5955,7 @@
       </c>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>Time Square</t>
+          <t>Times Square</t>
         </is>
       </c>
       <c r="K115" s="1" t="n">
@@ -6235,18 +5983,16 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116">
-        <f>+A116+1</f>
-        <v/>
+      <c r="A116" t="n">
+        <v>105</v>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D116" s="1">
-        <f>1+D116</f>
-        <v/>
+      <c r="D116" s="1" t="n">
+        <v>34</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -6260,7 +6006,7 @@
       </c>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>Time Square</t>
+          <t>Times Square</t>
         </is>
       </c>
       <c r="K116" s="1" t="n">
@@ -6288,18 +6034,16 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117">
-        <f>+A117+1</f>
-        <v/>
+      <c r="A117" t="n">
+        <v>106</v>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D117" s="1">
-        <f>1+D117</f>
-        <v/>
+      <c r="D117" s="1" t="n">
+        <v>35</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -6313,7 +6057,7 @@
       </c>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>Time Square</t>
+          <t>Times Square</t>
         </is>
       </c>
       <c r="K117" s="1" t="n">
@@ -6341,18 +6085,16 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118">
-        <f>+A118+1</f>
-        <v/>
+      <c r="A118" t="n">
+        <v>107</v>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D118" s="1">
-        <f>1+D118</f>
-        <v/>
+      <c r="D118" s="1" t="n">
+        <v>36</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -6394,18 +6136,16 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119">
-        <f>+A119+1</f>
-        <v/>
+      <c r="A119" t="n">
+        <v>108</v>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D119" s="1">
-        <f>1+D119</f>
-        <v/>
+      <c r="D119" s="1" t="n">
+        <v>37</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -6447,18 +6187,16 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120">
-        <f>+A120+1</f>
-        <v/>
+      <c r="A120" t="n">
+        <v>109</v>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D120" s="1">
-        <f>1+D120</f>
-        <v/>
+      <c r="D120" s="1" t="n">
+        <v>38</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -6500,18 +6238,16 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121">
-        <f>+A121+1</f>
-        <v/>
+      <c r="A121" t="n">
+        <v>110</v>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
           <t>Industrious</t>
         </is>
       </c>
-      <c r="D121" s="1">
-        <f>1+D121</f>
-        <v/>
+      <c r="D121" s="1" t="n">
+        <v>39</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -6553,10 +6289,6 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122">
-        <f>+A122+1</f>
-        <v/>
-      </c>
       <c r="M122" s="8" t="n"/>
       <c r="Q122" t="inlineStr">
         <is>
@@ -6565,9 +6297,8 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123">
-        <f>+A123+1</f>
-        <v/>
+      <c r="A123" t="n">
+        <v>111</v>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
@@ -6622,18 +6353,16 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124">
-        <f>+A124+1</f>
-        <v/>
+      <c r="A124" t="n">
+        <v>112</v>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D124" s="1">
-        <f>1+D124</f>
-        <v/>
+      <c r="D124" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -6670,18 +6399,16 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125">
-        <f>+A125+1</f>
-        <v/>
+      <c r="A125" t="n">
+        <v>113</v>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D125" s="1">
-        <f>1+D125</f>
-        <v/>
+      <c r="D125" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="E125" s="23" t="inlineStr">
         <is>
@@ -6718,18 +6445,16 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126">
-        <f>+A126+1</f>
-        <v/>
+      <c r="A126" t="n">
+        <v>114</v>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D126" s="1">
-        <f>1+D126</f>
-        <v/>
+      <c r="D126" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -6766,18 +6491,16 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127">
-        <f>+A127+1</f>
-        <v/>
+      <c r="A127" t="n">
+        <v>115</v>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D127" s="1">
-        <f>1+D127</f>
-        <v/>
+      <c r="D127" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -6814,18 +6537,16 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128">
-        <f>+A128+1</f>
-        <v/>
+      <c r="A128" t="n">
+        <v>116</v>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D128" s="1">
-        <f>1+D128</f>
-        <v/>
+      <c r="D128" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -6839,7 +6560,7 @@
       </c>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Flatiron District</t>
         </is>
       </c>
       <c r="K128" s="1" t="n">
@@ -6862,18 +6583,16 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129">
-        <f>+A129+1</f>
-        <v/>
+      <c r="A129" t="n">
+        <v>117</v>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D129" s="1">
-        <f>1+D129</f>
-        <v/>
+      <c r="D129" s="1" t="n">
+        <v>7</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -6910,18 +6629,16 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130">
-        <f>+A130+1</f>
-        <v/>
+      <c r="A130" t="n">
+        <v>118</v>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D130" s="1">
-        <f>1+D130</f>
-        <v/>
+      <c r="D130" s="1" t="n">
+        <v>8</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -6958,18 +6675,16 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131">
-        <f>+A131+1</f>
-        <v/>
+      <c r="A131" t="n">
+        <v>119</v>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D131" s="1">
-        <f>1+D131</f>
-        <v/>
+      <c r="D131" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -7006,18 +6721,16 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132">
-        <f>+A132+1</f>
-        <v/>
+      <c r="A132" t="n">
+        <v>120</v>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D132" s="1">
-        <f>1+D132</f>
-        <v/>
+      <c r="D132" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -7054,18 +6767,16 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133">
-        <f>+A133+1</f>
-        <v/>
+      <c r="A133" t="n">
+        <v>121</v>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D133" s="1">
-        <f>1+D133</f>
-        <v/>
+      <c r="D133" s="1" t="n">
+        <v>11</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -7102,18 +6813,16 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134">
-        <f>+A134+1</f>
-        <v/>
+      <c r="A134" t="n">
+        <v>122</v>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D134" s="1">
-        <f>1+D134</f>
-        <v/>
+      <c r="D134" s="1" t="n">
+        <v>12</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -7150,18 +6859,16 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135">
-        <f>+A135+1</f>
-        <v/>
+      <c r="A135" t="n">
+        <v>123</v>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D135" s="1">
-        <f>1+D135</f>
-        <v/>
+      <c r="D135" s="1" t="n">
+        <v>13</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -7198,18 +6905,16 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136">
-        <f>+A136+1</f>
-        <v/>
+      <c r="A136" t="n">
+        <v>124</v>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D136" s="1">
-        <f>1+D136</f>
-        <v/>
+      <c r="D136" s="1" t="n">
+        <v>14</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -7246,18 +6951,16 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137">
-        <f>+A137+1</f>
-        <v/>
+      <c r="A137" t="n">
+        <v>125</v>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D137" s="1">
-        <f>1+D137</f>
-        <v/>
+      <c r="D137" s="1" t="n">
+        <v>15</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -7294,18 +6997,16 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138">
-        <f>+A138+1</f>
-        <v/>
+      <c r="A138" t="n">
+        <v>126</v>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D138" s="1">
-        <f>1+D138</f>
-        <v/>
+      <c r="D138" s="1" t="n">
+        <v>16</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -7342,18 +7043,16 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139">
-        <f>+A139+1</f>
-        <v/>
+      <c r="A139" t="n">
+        <v>127</v>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D139" s="1">
-        <f>1+D139</f>
-        <v/>
+      <c r="D139" s="1" t="n">
+        <v>17</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -7390,18 +7089,16 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140">
-        <f>+A140+1</f>
-        <v/>
+      <c r="A140" t="n">
+        <v>128</v>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D140" s="1">
-        <f>1+D140</f>
-        <v/>
+      <c r="D140" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -7438,18 +7135,16 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141">
-        <f>+A141+1</f>
-        <v/>
+      <c r="A141" t="n">
+        <v>129</v>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D141" s="1">
-        <f>1+D141</f>
-        <v/>
+      <c r="D141" s="1" t="n">
+        <v>19</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -7486,18 +7181,16 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142">
-        <f>+A142+1</f>
-        <v/>
+      <c r="A142" t="n">
+        <v>130</v>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D142" s="1">
-        <f>1+D142</f>
-        <v/>
+      <c r="D142" s="1" t="n">
+        <v>20</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -7534,18 +7227,16 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143">
-        <f>+A143+1</f>
-        <v/>
+      <c r="A143" t="n">
+        <v>131</v>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D143" s="1">
-        <f>1+D143</f>
-        <v/>
+      <c r="D143" s="1" t="n">
+        <v>21</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -7582,18 +7273,16 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144">
-        <f>+A144+1</f>
-        <v/>
+      <c r="A144" t="n">
+        <v>132</v>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D144" s="1">
-        <f>1+D144</f>
-        <v/>
+      <c r="D144" s="1" t="n">
+        <v>22</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -7630,18 +7319,16 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145">
-        <f>+A145+1</f>
-        <v/>
+      <c r="A145" t="n">
+        <v>133</v>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D145" s="1">
-        <f>1+D145</f>
-        <v/>
+      <c r="D145" s="1" t="n">
+        <v>23</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -7678,18 +7365,16 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146">
-        <f>+A146+1</f>
-        <v/>
+      <c r="A146" t="n">
+        <v>134</v>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D146" s="1">
-        <f>1+D146</f>
-        <v/>
+      <c r="D146" s="1" t="n">
+        <v>24</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -7726,18 +7411,16 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147">
-        <f>+A147+1</f>
-        <v/>
+      <c r="A147" t="n">
+        <v>135</v>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D147" s="1">
-        <f>1+D147</f>
-        <v/>
+      <c r="D147" s="1" t="n">
+        <v>25</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -7774,18 +7457,16 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148">
-        <f>+A148+1</f>
-        <v/>
+      <c r="A148" t="n">
+        <v>136</v>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D148" s="1">
-        <f>1+D148</f>
-        <v/>
+      <c r="D148" s="1" t="n">
+        <v>26</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -7822,18 +7503,16 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149">
-        <f>+A149+1</f>
-        <v/>
+      <c r="A149" t="n">
+        <v>137</v>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D149" s="1">
-        <f>1+D149</f>
-        <v/>
+      <c r="D149" s="1" t="n">
+        <v>27</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -7870,18 +7549,16 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150">
-        <f>+A150+1</f>
-        <v/>
+      <c r="A150" t="n">
+        <v>138</v>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D150" s="1">
-        <f>1+D150</f>
-        <v/>
+      <c r="D150" s="1" t="n">
+        <v>28</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -7918,18 +7595,16 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151">
-        <f>+A151+1</f>
-        <v/>
+      <c r="A151" t="n">
+        <v>139</v>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D151" s="1">
-        <f>1+D151</f>
-        <v/>
+      <c r="D151" s="1" t="n">
+        <v>29</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -7966,18 +7641,16 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152">
-        <f>+A152+1</f>
-        <v/>
+      <c r="A152" t="n">
+        <v>140</v>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
       </c>
-      <c r="D152" s="1">
-        <f>1+D152</f>
-        <v/>
+      <c r="D152" s="1" t="n">
+        <v>30</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -8014,16 +7687,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153">
-        <f>+A153+1</f>
-        <v/>
-      </c>
       <c r="M153" s="8" t="n"/>
     </row>
     <row r="154">
-      <c r="A154">
-        <f>+A154+1</f>
-        <v/>
+      <c r="A154" t="n">
+        <v>141</v>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
@@ -8045,7 +7713,7 @@
       </c>
       <c r="I154" s="1" t="inlineStr">
         <is>
-          <t>Downtown</t>
+          <t>World Trade Center</t>
         </is>
       </c>
       <c r="K154" s="1" t="n">
@@ -8078,18 +7746,16 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155">
-        <f>+A155+1</f>
-        <v/>
+      <c r="A155" t="n">
+        <v>142</v>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
           <t>Servcorp</t>
         </is>
       </c>
-      <c r="D155" s="1">
-        <f>1+D155</f>
-        <v/>
+      <c r="D155" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
@@ -8131,18 +7797,16 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156">
-        <f>+A156+1</f>
-        <v/>
+      <c r="A156" t="n">
+        <v>143</v>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
           <t>Servcorp</t>
         </is>
       </c>
-      <c r="D156" s="1">
-        <f>1+D156</f>
-        <v/>
+      <c r="D156" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
@@ -8179,16 +7843,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157">
-        <f>+A157+1</f>
-        <v/>
-      </c>
       <c r="M157" s="8" t="n"/>
     </row>
     <row r="158">
-      <c r="A158">
-        <f>+A158+1</f>
-        <v/>
+      <c r="A158" t="n">
+        <v>144</v>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
@@ -8238,18 +7897,16 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159">
-        <f>+A159+1</f>
-        <v/>
+      <c r="A159" t="n">
+        <v>145</v>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
           <t>Emerge212 / Elevated</t>
         </is>
       </c>
-      <c r="D159" s="1">
-        <f>1+D159</f>
-        <v/>
+      <c r="D159" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
@@ -8291,18 +7948,16 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160">
-        <f>+A160+1</f>
-        <v/>
+      <c r="A160" t="n">
+        <v>146</v>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
           <t>Emerge212 / Elevated</t>
         </is>
       </c>
-      <c r="D160" s="1">
-        <f>1+D160</f>
-        <v/>
+      <c r="D160" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
@@ -8339,16 +7994,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161">
-        <f>+A161+1</f>
-        <v/>
-      </c>
       <c r="M161" s="8" t="n"/>
     </row>
     <row r="162">
-      <c r="A162">
-        <f>+A162+1</f>
-        <v/>
+      <c r="A162" t="n">
+        <v>147</v>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
@@ -8398,18 +8048,16 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163">
-        <f>+A163+1</f>
-        <v/>
+      <c r="A163" t="n">
+        <v>148</v>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
           <t>Inspire Workspace</t>
         </is>
       </c>
-      <c r="D163" s="1">
-        <f>1+D163</f>
-        <v/>
+      <c r="D163" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
@@ -8446,16 +8094,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164">
-        <f>+A164+1</f>
-        <v/>
-      </c>
       <c r="M164" s="8" t="n"/>
     </row>
     <row r="165">
-      <c r="A165">
-        <f>+A165+1</f>
-        <v/>
+      <c r="A165" t="n">
+        <v>149</v>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
@@ -8510,18 +8153,16 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166">
-        <f>+A166+1</f>
-        <v/>
+      <c r="A166" t="n">
+        <v>150</v>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
           <t>Stark Office Suites</t>
         </is>
       </c>
-      <c r="D166" s="1">
-        <f>1+D166</f>
-        <v/>
+      <c r="D166" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
@@ -8563,18 +8204,16 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167">
-        <f>+A167+1</f>
-        <v/>
+      <c r="A167" t="n">
+        <v>151</v>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
           <t>Excelsior (high end)</t>
         </is>
       </c>
-      <c r="D167" s="1">
-        <f>1+D167</f>
-        <v/>
+      <c r="D167" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
@@ -8611,18 +8250,16 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168">
-        <f>+A168+1</f>
-        <v/>
+      <c r="A168" t="n">
+        <v>152</v>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
           <t>Excelsior (high end)</t>
         </is>
       </c>
-      <c r="D168" s="1">
-        <f>1+D168</f>
-        <v/>
+      <c r="D168" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
@@ -8659,16 +8296,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169">
-        <f>+A169+1</f>
-        <v/>
-      </c>
       <c r="M169" s="8" t="n"/>
     </row>
     <row r="170">
-      <c r="A170">
-        <f>+A170+1</f>
-        <v/>
+      <c r="A170" t="n">
+        <v>153</v>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
@@ -8733,18 +8365,16 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171">
-        <f>+A171+1</f>
-        <v/>
+      <c r="A171" t="n">
+        <v>154</v>
       </c>
       <c r="C171" s="1" t="inlineStr">
         <is>
           <t>Helix Workspace</t>
         </is>
       </c>
-      <c r="D171" s="1">
-        <f>1+D171</f>
-        <v/>
+      <c r="D171" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
@@ -8791,16 +8421,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172">
-        <f>+A172+1</f>
-        <v/>
-      </c>
       <c r="M172" s="8" t="n"/>
     </row>
     <row r="173">
-      <c r="A173">
-        <f>+A173+1</f>
-        <v/>
+      <c r="A173" t="n">
+        <v>155</v>
       </c>
       <c r="C173" s="1" t="inlineStr">
         <is>
@@ -8860,18 +8485,16 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174">
-        <f>+A174+1</f>
-        <v/>
+      <c r="A174" t="n">
+        <v>156</v>
       </c>
       <c r="C174" s="1" t="inlineStr">
         <is>
           <t>TKO Suites</t>
         </is>
       </c>
-      <c r="D174" s="1">
-        <f>+D174+1</f>
-        <v/>
+      <c r="D174" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
@@ -8913,18 +8536,16 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175">
-        <f>+A175+1</f>
-        <v/>
+      <c r="A175" t="n">
+        <v>157</v>
       </c>
       <c r="C175" s="1" t="inlineStr">
         <is>
           <t>TKO Suites</t>
         </is>
       </c>
-      <c r="D175" s="1">
-        <f>+D175+1</f>
-        <v/>
+      <c r="D175" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
@@ -8961,18 +8582,16 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176">
-        <f>+A176+1</f>
-        <v/>
+      <c r="A176" t="n">
+        <v>158</v>
       </c>
       <c r="C176" s="1" t="inlineStr">
         <is>
           <t>TKO Suites</t>
         </is>
       </c>
-      <c r="D176" s="1">
-        <f>+D176+1</f>
-        <v/>
+      <c r="D176" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
@@ -9009,16 +8628,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177">
-        <f>+A177+1</f>
-        <v/>
-      </c>
       <c r="M177" s="8" t="n"/>
     </row>
     <row r="178">
-      <c r="A178">
-        <f>+A178+1</f>
-        <v/>
+      <c r="A178" t="n">
+        <v>159</v>
       </c>
       <c r="C178" s="1" t="inlineStr">
         <is>
@@ -9078,10 +8692,6 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179">
-        <f>+A179+1</f>
-        <v/>
-      </c>
       <c r="M179" s="8" t="n"/>
       <c r="Q179" t="inlineStr">
         <is>
@@ -9090,9 +8700,8 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180">
-        <f>+A180+1</f>
-        <v/>
+      <c r="A180" t="n">
+        <v>160</v>
       </c>
       <c r="C180" s="1" t="inlineStr">
         <is>
@@ -9145,18 +8754,16 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181">
-        <f>+A181+1</f>
-        <v/>
+      <c r="A181" t="n">
+        <v>161</v>
       </c>
       <c r="C181" s="1" t="inlineStr">
         <is>
           <t>Corporate Suites</t>
         </is>
       </c>
-      <c r="D181" s="1">
-        <f>+D181+1</f>
-        <v/>
+      <c r="D181" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
@@ -9198,18 +8805,16 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182">
-        <f>+A182+1</f>
-        <v/>
+      <c r="A182" t="n">
+        <v>162</v>
       </c>
       <c r="C182" s="1" t="inlineStr">
         <is>
           <t>Corporate Suites</t>
         </is>
       </c>
-      <c r="D182" s="1">
-        <f>+D182+1</f>
-        <v/>
+      <c r="D182" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
@@ -9251,18 +8856,16 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183">
-        <f>+A183+1</f>
-        <v/>
+      <c r="A183" t="n">
+        <v>163</v>
       </c>
       <c r="C183" s="1" t="inlineStr">
         <is>
           <t>Corporate Suites</t>
         </is>
       </c>
-      <c r="D183" s="1">
-        <f>+D183+1</f>
-        <v/>
+      <c r="D183" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -9309,10 +8912,6 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184">
-        <f>+A184+1</f>
-        <v/>
-      </c>
       <c r="M184" s="8" t="inlineStr">
         <is>
           <t>Paul Carter</t>
@@ -9330,14 +8929,8 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185">
-        <f>+A185+1</f>
-        <v/>
-      </c>
       <c r="C185" s="1" t="n"/>
-      <c r="D185" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="D185" s="1" t="n"/>
       <c r="G185" s="1" t="n"/>
       <c r="I185" s="1" t="n"/>
       <c r="K185" s="1" t="n"/>
@@ -9346,15 +8939,8 @@
       <c r="Q185" s="2" t="n"/>
     </row>
     <row r="186">
-      <c r="A186">
-        <f>+A186+1</f>
-        <v/>
-      </c>
       <c r="C186" s="1" t="n"/>
-      <c r="D186" s="1">
-        <f>+D186+1</f>
-        <v/>
-      </c>
+      <c r="D186" s="1" t="n"/>
       <c r="G186" s="1" t="n"/>
       <c r="I186" s="1" t="n"/>
       <c r="K186" s="1" t="n"/>
@@ -9362,16 +8948,11 @@
       <c r="O186" s="1" t="n"/>
     </row>
     <row r="187">
-      <c r="A187">
-        <f>+A187+1</f>
-        <v/>
-      </c>
       <c r="M187" s="8" t="n"/>
     </row>
     <row r="188">
-      <c r="A188">
-        <f>+A188+1</f>
-        <v/>
+      <c r="A188" t="n">
+        <v>164</v>
       </c>
       <c r="C188" s="1" t="inlineStr">
         <is>
@@ -9455,18 +9036,16 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189">
-        <f>+A189+1</f>
-        <v/>
+      <c r="A189" t="n">
+        <v>165</v>
       </c>
       <c r="C189" s="1" t="inlineStr">
         <is>
           <t>The Yard</t>
         </is>
       </c>
-      <c r="D189" s="1">
-        <f>+D189+1</f>
-        <v/>
+      <c r="D189" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -9523,18 +9102,16 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190">
-        <f>+A190+1</f>
-        <v/>
+      <c r="A190" t="n">
+        <v>166</v>
       </c>
       <c r="C190" s="1" t="inlineStr">
         <is>
           <t>The Yard</t>
         </is>
       </c>
-      <c r="D190" s="1">
-        <f>+D190+1</f>
-        <v/>
+      <c r="D190" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -9586,18 +9163,16 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191">
-        <f>+A191+1</f>
-        <v/>
+      <c r="A191" t="n">
+        <v>167</v>
       </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
           <t>The Yard</t>
         </is>
       </c>
-      <c r="D191" s="1">
-        <f>+D191+1</f>
-        <v/>
+      <c r="D191" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -9659,18 +9234,16 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192">
-        <f>+A192+1</f>
-        <v/>
+      <c r="A192" t="n">
+        <v>168</v>
       </c>
       <c r="C192" s="1" t="inlineStr">
         <is>
           <t>The Yard</t>
         </is>
       </c>
-      <c r="D192" s="1">
-        <f>+D192+1</f>
-        <v/>
+      <c r="D192" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -9727,18 +9300,16 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193">
-        <f>+A193+1</f>
-        <v/>
+      <c r="A193" t="n">
+        <v>169</v>
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
           <t>The Yard</t>
         </is>
       </c>
-      <c r="D193" s="1">
-        <f>+D193+1</f>
-        <v/>
+      <c r="D193" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -9795,18 +9366,16 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194">
-        <f>+A194+1</f>
-        <v/>
+      <c r="A194" t="n">
+        <v>170</v>
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
           <t>The Yard</t>
         </is>
       </c>
-      <c r="D194" s="1">
-        <f>+D194+1</f>
-        <v/>
+      <c r="D194" s="1" t="n">
+        <v>7</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -9863,18 +9432,16 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195">
-        <f>+A195+1</f>
-        <v/>
+      <c r="A195" t="n">
+        <v>171</v>
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
           <t>The Yard</t>
         </is>
       </c>
-      <c r="D195" s="1">
-        <f>+D195+1</f>
-        <v/>
+      <c r="D195" s="1" t="n">
+        <v>8</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -9931,100 +9498,42 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196">
-        <f>+A196+1</f>
-        <v/>
-      </c>
       <c r="M196" s="8" t="n"/>
     </row>
-    <row r="197">
-      <c r="A197">
-        <f>+A197+1</f>
-        <v/>
-      </c>
-    </row>
     <row r="198">
-      <c r="A198">
-        <f>+A198+1</f>
-        <v/>
-      </c>
       <c r="M198" s="8" t="n"/>
     </row>
     <row r="199">
-      <c r="A199">
-        <f>+A199+1</f>
-        <v/>
-      </c>
       <c r="M199" s="8" t="n"/>
     </row>
     <row r="200">
-      <c r="A200">
-        <f>+A200+1</f>
-        <v/>
-      </c>
       <c r="M200" s="8" t="n"/>
     </row>
     <row r="201">
-      <c r="A201">
-        <f>+A201+1</f>
-        <v/>
-      </c>
       <c r="M201" s="8" t="n"/>
     </row>
     <row r="202">
-      <c r="A202">
-        <f>+A202+1</f>
-        <v/>
-      </c>
       <c r="M202" s="8" t="n"/>
     </row>
     <row r="203">
-      <c r="A203">
-        <f>+A203+1</f>
-        <v/>
-      </c>
       <c r="M203" s="8" t="n"/>
     </row>
     <row r="204">
-      <c r="A204">
-        <f>+A204+1</f>
-        <v/>
-      </c>
       <c r="M204" s="8" t="n"/>
     </row>
     <row r="205">
-      <c r="A205">
-        <f>+A205+1</f>
-        <v/>
-      </c>
       <c r="M205" s="8" t="n"/>
     </row>
     <row r="206">
-      <c r="A206">
-        <f>+A206+1</f>
-        <v/>
-      </c>
       <c r="M206" s="8" t="n"/>
     </row>
     <row r="207">
-      <c r="A207">
-        <f>+A207+1</f>
-        <v/>
-      </c>
       <c r="M207" s="8" t="n"/>
     </row>
     <row r="208">
-      <c r="A208">
-        <f>+A208+1</f>
-        <v/>
-      </c>
       <c r="M208" s="8" t="n"/>
     </row>
     <row r="209">
-      <c r="A209">
-        <f>+A209+1</f>
-        <v/>
-      </c>
       <c r="M209" s="8" t="n"/>
     </row>
     <row r="210">
@@ -10191,7 +9700,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -10204,7 +9713,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>174</v>
+        <v>40</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -10244,7 +9753,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -10252,7 +9761,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>175</v>
+        <v>41</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -10292,7 +9801,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -10300,7 +9809,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>176</v>
+        <v>42</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -10340,7 +9849,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -10348,7 +9857,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>177</v>
+        <v>43</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -10389,7 +9898,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -10397,7 +9906,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>178</v>
+        <v>44</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -10438,7 +9947,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -10446,7 +9955,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>179</v>
+        <v>45</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -10487,7 +9996,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -10500,7 +10009,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>180</v>
+        <v>46</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -10540,7 +10049,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -10548,7 +10057,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>181</v>
+        <v>47</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -10588,7 +10097,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -10596,7 +10105,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -10637,7 +10146,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -10650,7 +10159,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>183</v>
+        <v>49</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -10690,7 +10199,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -10698,7 +10207,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>184</v>
+        <v>50</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -10738,7 +10247,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -10746,7 +10255,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>185</v>
+        <v>51</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -10787,7 +10296,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -10800,7 +10309,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>186</v>
+        <v>52</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -10840,7 +10349,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -10848,7 +10357,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>187</v>
+        <v>53</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -10888,7 +10397,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -10901,7 +10410,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -10941,7 +10450,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -10954,7 +10463,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>189</v>
+        <v>55</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -10994,7 +10503,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -11002,7 +10511,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -11042,7 +10551,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -11050,7 +10559,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>191</v>
+        <v>57</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -11090,7 +10599,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -11103,7 +10612,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>192</v>
+        <v>58</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -11143,7 +10652,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -11156,7 +10665,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>193</v>
+        <v>59</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -11196,7 +10705,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -11204,7 +10713,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>194</v>
+        <v>60</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -11245,7 +10754,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -11253,7 +10762,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>195</v>
+        <v>61</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -11293,7 +10802,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -11301,7 +10810,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>196</v>
+        <v>62</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -11341,7 +10850,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -11354,7 +10863,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>197</v>
+        <v>63</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -11394,7 +10903,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -11402,7 +10911,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>198</v>
+        <v>64</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -11443,7 +10952,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -11451,7 +10960,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>199</v>
+        <v>65</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -11491,7 +11000,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -11499,7 +11008,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>200</v>
+        <v>66</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -11540,7 +11049,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -11548,7 +11057,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>201</v>
+        <v>67</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -11589,7 +11098,7 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -11597,7 +11106,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>202</v>
+        <v>68</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -11638,7 +11147,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -11646,7 +11155,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>203</v>
+        <v>69</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -11686,7 +11195,7 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -11694,7 +11203,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>204</v>
+        <v>70</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -11734,7 +11243,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -11742,7 +11251,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>205</v>
+        <v>71</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -11782,7 +11291,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -11790,7 +11299,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>206</v>
+        <v>72</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -11830,7 +11339,7 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -11838,7 +11347,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>207</v>
+        <v>73</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -11878,7 +11387,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -11886,7 +11395,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>208</v>
+        <v>74</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -11926,7 +11435,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -11934,7 +11443,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -11975,7 +11484,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -11983,7 +11492,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -12024,7 +11533,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -12032,7 +11541,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -12073,7 +11582,7 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -12081,7 +11590,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>212</v>
+        <v>78</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -12122,7 +11631,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -12130,7 +11639,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>213</v>
+        <v>79</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -12172,7 +11681,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -12180,7 +11689,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>214</v>
+        <v>80</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -12221,7 +11730,7 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -12229,7 +11738,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>215</v>
+        <v>81</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -12269,7 +11778,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -12277,7 +11786,7 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>216</v>
+        <v>82</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -12318,7 +11827,7 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
@@ -12331,7 +11840,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -12373,7 +11882,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -12381,7 +11890,7 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>218</v>
+        <v>84</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -12423,7 +11932,7 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -12431,7 +11940,7 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>219</v>
+        <v>85</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -12473,12 +11982,15 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
+      </c>
+      <c r="D310" t="n">
+        <v>31</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -12514,12 +12026,15 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
           <t>WeWork</t>
         </is>
+      </c>
+      <c r="D311" t="n">
+        <v>32</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -12555,12 +12070,15 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
           <t>Select Office Suites</t>
         </is>
+      </c>
+      <c r="D312" t="n">
+        <v>1</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -12613,12 +12131,15 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
           <t>Select Office Suites</t>
         </is>
+      </c>
+      <c r="D313" t="n">
+        <v>2</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>

--- a/Office_Suites_NYC.xlsx
+++ b/Office_Suites_NYC.xlsx
@@ -3188,7 +3188,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>159 West 25th street, floor 4, 5, 7, &amp; 8</t>
+          <t>159 West 25th Street, Floor 4, 5, 7, &amp; 8</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>he shows space and I don’t need to be present, 4th floor is currenly has spaces on iy</t>
+          <t>he shows space and I don’t need to be present, 4th floor currently has spaces on it</t>
         </is>
       </c>
       <c r="AE81" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>902 Braodway (June 2026 opening)</t>
+          <t>902 Broadway (June 2026 opening)</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>390 park Avenue (June 2026 opening)</t>
+          <t>390 Park Avenue (June 2026 opening)</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>215 Park Avnue South</t>
+          <t>215 Park Avenue South</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
@@ -5878,7 +5878,11 @@
       <c r="K113" s="1" t="n"/>
       <c r="M113" s="8" t="n"/>
       <c r="O113" s="1" t="n"/>
-      <c r="Q113" s="2" t="n"/>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>mailto:brokers@industriousoffice.com</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7240,7 +7244,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>575 Fith Avenue</t>
+          <t>575 Fifth Avenue</t>
         </is>
       </c>
       <c r="G143" s="1" t="inlineStr">
@@ -7938,7 +7942,7 @@
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>I don’t need to show space - cleitn can go direct</t>
+          <t>I don’t need to show space - client can go direct</t>
         </is>
       </c>
       <c r="AE159" t="inlineStr">
@@ -8744,8 +8748,10 @@
           <t>pcarter@corporatesuites.com</t>
         </is>
       </c>
-      <c r="U180" s="21" t="n">
-        <v>0.1</v>
+      <c r="U180" s="21" t="inlineStr">
+        <is>
+          <t>10% per year</t>
+        </is>
       </c>
       <c r="AE180" t="inlineStr">
         <is>
@@ -8902,7 +8908,7 @@
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>2 mos concious</t>
+          <t>2 months concession</t>
         </is>
       </c>
       <c r="AE183" t="inlineStr">

--- a/Office_Suites_NYC.xlsx
+++ b/Office_Suites_NYC.xlsx
@@ -4390,7 +4390,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>902 Broadway (June 2026 opening)</t>
+          <t>902 Broadway</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>386 Park Avenue South  (June 2026 opening)</t>
+          <t>386 Park Avenue South</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>875 Third Avenue (June 2026 opening)</t>
+          <t>875 Third Avenue</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>390 Park Avenue (June 2026 opening)</t>
+          <t>390 Park Avenue</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>717 Fifth Avenue, Floor 12A and 14 (opening in August 26)</t>
+          <t>717 Fifth Avenue, Floor 12A and 14</t>
         </is>
       </c>
       <c r="G168" s="1" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">613 East 34th Street (opening up August 1), </t>
+          <t>613 East 34th Street</t>
         </is>
       </c>
       <c r="G183" s="1" t="inlineStr">
